--- a/TestDatas/user_api_cases.xlsx
+++ b/TestDatas/user_api_cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -509,6 +509,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>是否鉴权</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,8 +536,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>{"$[0].id": "1", "$[0].name": "Leanne Graham"}</t>
@@ -553,8 +556,6 @@
           <t>first_user_id</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -568,6 +569,11 @@
       <c r="O2" t="inlineStr">
         <is>
           <t>验证用户列表接口可访问</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -592,8 +598,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>{"$.id": "1", "$.name": "Leanne Graham"}</t>
@@ -614,8 +618,6 @@
           <t>user_email</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -629,6 +631,11 @@
       <c r="O3" t="inlineStr">
         <is>
           <t>验证单用户查询</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -653,8 +660,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>{"$[0].userId": "1", "$[0].id": "1"}</t>
@@ -675,8 +680,6 @@
           <t>first_post_id</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -690,6 +693,11 @@
       <c r="O4" t="inlineStr">
         <is>
           <t>验证用户帖子查询</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -744,8 +752,6 @@
           <t>new_post_id</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -759,6 +765,11 @@
       <c r="O5" t="inlineStr">
         <is>
           <t>验证创建帖子接口</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -783,8 +794,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>{"$.userId": "1"}</t>
@@ -795,10 +804,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Y</t>
@@ -812,6 +817,11 @@
       <c r="O6" t="inlineStr">
         <is>
           <t>验证#变量#替换功能</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -856,10 +866,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Y</t>
@@ -873,6 +879,11 @@
       <c r="O7" t="inlineStr">
         <is>
           <t>验证PUT更新操作</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -897,18 +908,11 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -922,6 +926,11 @@
       <c r="O8" t="inlineStr">
         <is>
           <t>验证DELETE删除操作</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -946,8 +955,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>{"$[0].id": "1", "$[0].postId": "1"}</t>
@@ -958,10 +965,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Y</t>
@@ -975,6 +978,11 @@
       <c r="O9" t="inlineStr">
         <is>
           <t>验证评论查询接口</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -999,8 +1007,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>{"$[0].userId": "1", "$[0].id": "1"}</t>
@@ -1011,10 +1017,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1028,6 +1030,11 @@
       <c r="O10" t="inlineStr">
         <is>
           <t>验证相册列表接口</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1052,8 +1059,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>{"$[0].userId": "1", "$[0].id": "1"}</t>
@@ -1064,10 +1069,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1081,6 +1082,11 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>验证TODO列表接口</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1105,18 +1111,11 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>N</t>
@@ -1130,6 +1129,11 @@
       <c r="O12" t="inlineStr">
         <is>
           <t>此用例不参与执行</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
